--- a/02_Zero_Shot/outputs/NLI/DeBERTa-v3-large/RESULT_clap_deberta-v3-large_zeroshot.xlsx
+++ b/02_Zero_Shot/outputs/NLI/DeBERTa-v3-large/RESULT_clap_deberta-v3-large_zeroshot.xlsx
@@ -12682,7 +12682,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -22270,7 +22270,7 @@
       </c>
       <c r="C1285" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>BUG</t>
         </is>
       </c>
     </row>
@@ -23494,7 +23494,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>FEATURE</t>
+          <t>OTHER</t>
         </is>
       </c>
     </row>
@@ -51479,7 +51479,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5793333333333334</v>
+        <v>0.5796666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -51489,7 +51489,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4598585803290547</v>
+        <v>0.4600199908149294</v>
       </c>
     </row>
     <row r="4">
@@ -51499,7 +51499,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5796483470940761</v>
+        <v>0.5799671288894752</v>
       </c>
     </row>
     <row r="5">
@@ -51509,7 +51509,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4569692435191475</v>
+        <v>0.4570290425654897</v>
       </c>
     </row>
     <row r="6">
@@ -51519,7 +51519,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5394804916490837</v>
+        <v>0.5395754133386899</v>
       </c>
     </row>
     <row r="7">
@@ -51529,7 +51529,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>649.196996484</v>
+        <v>837.774103224001</v>
       </c>
     </row>
     <row r="8">
@@ -51539,7 +51539,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.216398998828</v>
+        <v>0.2792580344080003</v>
       </c>
     </row>
   </sheetData>
